--- a/timepoint-assignment/test_visits.xlsx
+++ b/timepoint-assignment/test_visits.xlsx
@@ -558,7 +558,7 @@
         <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>240</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -701,9 +701,7 @@
       <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" t="n">
-        <v>25</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>PDF: lands in T2</t>
